--- a/data/b2_bonsucesso/B2 Bonsucesso 07-2026.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 07-2026.xlsx
@@ -4905,110 +4905,110 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46205</v>
+        <v>46208</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>2438.68</v>
+        <v>64627.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1076.6</v>
+        <v>3112.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46208</v>
+        <v>46210</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>65219.49</v>
+        <v>1066.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46208</v>
+        <v>46211</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3006.82</v>
+        <v>1170.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46208</v>
+        <v>46213</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3095.83</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3600</v>
+        <v>4541.38</v>
       </c>
     </row>
     <row r="8">
@@ -5017,34 +5017,34 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>4708.44</v>
+        <v>1227.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1240.95</v>
+        <v>2577.61</v>
       </c>
     </row>
     <row r="10">
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>10466.52</v>
+        <v>9213.34</v>
       </c>
     </row>
     <row r="11">
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>2060.09</v>
+        <v>2188.44</v>
       </c>
     </row>
     <row r="12">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>4476.99</v>
+        <v>4321.54</v>
       </c>
     </row>
     <row r="13">
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>22734.67</v>
+        <v>22453.42</v>
       </c>
     </row>
     <row r="14">
@@ -5134,25 +5134,25 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1186.93</v>
+        <v>1160.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1015.77</v>
+        <v>1511.46</v>
       </c>
     </row>
     <row r="16">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>4376.37</v>
+        <v>4459.95</v>
       </c>
     </row>
     <row r="17">
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3165.47</v>
+        <v>3173.83</v>
       </c>
     </row>
   </sheetData>
